--- a/data/export/2026-09-24-182路.xlsx
+++ b/data/export/2026-09-24-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC10"/>
+  <dimension ref="A1:AC15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -441,7 +441,7 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
@@ -632,32 +632,36 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:18</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -665,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -689,33 +693,37 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>2/12</t>
         </is>
       </c>
     </row>
@@ -743,32 +751,36 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -776,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -800,17 +812,17 @@
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
@@ -820,13 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>71.0</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>1/12</t>
         </is>
       </c>
     </row>
@@ -887,7 +903,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -926,7 +942,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -937,7 +953,7 @@
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -998,7 +1014,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1048,7 +1064,7 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -1076,32 +1092,36 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:56</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1109,7 +1129,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1133,17 +1153,17 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
@@ -1153,13 +1173,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>3/12</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1244,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1270,7 +1294,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1355,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1381,7 +1405,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1466,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1492,7 +1516,7 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/12</t>
         </is>
       </c>
     </row>
@@ -1500,22 +1524,22 @@
       <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>沪A67353D</t>
+          <t>沪A66513D</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>07:12</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>07:15</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1548,12 +1572,12 @@
       <c r="M10" s="2" t="inlineStr"/>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:41</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1567,7 +1591,7 @@
       <c r="T10" s="2" t="inlineStr"/>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>07:15</t>
+          <t>07:12</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
@@ -1603,7 +1627,566 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/9</t>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>07:24</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>07:35</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>2/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>07:36</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>07:36</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>—/12</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-24-182路.xlsx
+++ b/data/export/2026-09-24-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC15"/>
+  <dimension ref="A1:AC25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -642,19 +642,19 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>07:18</t>
+          <t>07:24</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>2/12</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -761,24 +761,24 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>07:21</t>
+          <t>07:23</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>71.0</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>1/12</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -870,32 +870,36 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:36</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -903,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -927,17 +931,17 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
@@ -947,13 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -981,32 +989,36 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:02</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1014,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1038,33 +1050,37 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1102,24 +1118,24 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>07:56</t>
+          <t>07:53</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1129,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1168,22 +1184,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>3/12</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1211,32 +1227,36 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -1244,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1268,33 +1288,37 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1322,32 +1346,36 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:26</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1355,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1379,33 +1407,37 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1433,32 +1465,36 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:29</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -1466,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1490,33 +1526,37 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1577,7 +1617,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>07:01</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1616,7 +1656,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1627,7 +1667,7 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -1655,32 +1695,36 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:51</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1688,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1712,33 +1756,37 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>96.0</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1799,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1849,7 +1897,7 @@
       <c r="AB12" s="2" t="inlineStr"/>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -1910,7 +1958,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1959,12 +2007,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>2/12</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2025,7 +2073,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2075,7 +2123,7 @@
       <c r="AB14" s="2" t="inlineStr"/>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/14</t>
         </is>
       </c>
     </row>
@@ -2083,22 +2131,22 @@
       <c r="A15" s="2" t="inlineStr"/>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>沪A68397D</t>
+          <t>沪A08953A</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>07:48</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>07:55</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -2131,12 +2179,12 @@
       <c r="M15" s="2" t="inlineStr"/>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>07:21</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>08:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2150,7 +2198,7 @@
       <c r="T15" s="2" t="inlineStr"/>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>07:55</t>
+          <t>07:48</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
@@ -2175,7 +2223,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2186,7 +2234,1149 @@
       <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/12</t>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>07:55</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>08:00</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>73.0</t>
+        </is>
+      </c>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>08:15</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>沪A12050A</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>08:31</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>06:12</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>08:35</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>沪A02126A</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>—/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>96.0</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-24-182路.xlsx
+++ b/data/export/2026-09-24-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC25"/>
+  <dimension ref="A1:AC31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,17 +946,17 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1584,32 +1584,36 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:37</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -1617,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1641,17 +1645,17 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
@@ -1661,13 +1665,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1705,12 +1713,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>08:51</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96分钟</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
@@ -1732,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1781,12 +1789,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1814,32 +1822,36 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1847,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:11</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1871,33 +1883,37 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1925,32 +1941,36 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -1958,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1982,37 +2002,37 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2040,32 +2060,36 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -2073,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2097,33 +2121,37 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2151,32 +2179,36 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -2184,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2208,33 +2240,37 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2262,32 +2298,36 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:27</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -2295,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2319,32 +2359,32 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2377,32 +2417,36 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -2410,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2434,17 +2478,17 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
@@ -2454,17 +2498,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2492,32 +2536,36 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -2525,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2549,37 +2597,37 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2640,7 +2688,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2694,7 +2742,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -2755,7 +2803,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2866,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2920,7 +2968,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2981,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3035,7 +3083,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3096,7 +3144,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3150,7 +3198,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3211,7 +3259,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3255,13 +3303,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB24" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3322,7 +3374,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:21</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3371,12 +3423,702 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>97.0</t>
+        </is>
+      </c>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>13/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>09:35</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>10/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>沪A08953A</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>11/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>88.5</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-24-182路.xlsx
+++ b/data/export/2026-09-24-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC31"/>
+  <dimension ref="A1:AC39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,14 +827,14 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
           <t>84.0</t>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,22 +1184,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,22 +1303,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,22 +1422,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1546,17 +1546,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,22 +1660,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,22 +1779,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2493,14 +2493,14 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
           <t>84.0</t>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2546,24 +2546,24 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2622,12 +2622,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2655,32 +2655,36 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -2688,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2712,37 +2716,37 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2770,32 +2774,36 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
           <t>07:51</t>
@@ -2803,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2827,33 +2835,37 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB20" s="2" t="inlineStr"/>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>—/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -2881,32 +2893,36 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -2914,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2938,37 +2954,37 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2996,32 +3012,36 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:06</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3029,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3053,37 +3073,37 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3111,32 +3131,36 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -3144,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:02</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3168,17 +3192,17 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
@@ -3188,17 +3212,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -3226,32 +3250,36 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -3259,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3283,37 +3311,37 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -3341,32 +3369,36 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:25</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3374,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3398,37 +3430,37 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3489,7 +3521,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:11</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3543,7 +3575,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -3604,7 +3636,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3658,7 +3690,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3719,7 +3751,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3758,7 +3790,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3773,7 +3805,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3834,7 +3866,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3888,7 +3920,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -3949,7 +3981,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4003,7 +4035,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -4011,22 +4043,22 @@
       <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>沪A31073D</t>
+          <t>沪A55712D</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>10:15</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -4064,7 +4096,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>10:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4078,47 +4110,967 @@
       <c r="T31" s="2" t="inlineStr"/>
       <c r="U31" s="2" t="inlineStr">
         <is>
+          <t>10:05</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
           <t>10:15</t>
         </is>
       </c>
-      <c r="V31" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>10:15</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W31" s="2" t="inlineStr">
+      <c r="W32" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X31" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y31" s="2" t="inlineStr">
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z31" s="2" t="inlineStr">
+      <c r="Z32" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
+      <c r="AA32" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB31" s="2" t="inlineStr">
-        <is>
-          <t>88.5</t>
-        </is>
-      </c>
-      <c r="AC31" s="2" t="inlineStr">
-        <is>
-          <t>7/14</t>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>11/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>79.5</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>沪A12050A</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>06:12</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>10:50</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>83.5</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>78.5</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>11:05</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>10:21</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>12/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-24-182路.xlsx
+++ b/data/export/2026-09-24-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC39"/>
+  <dimension ref="A1:AC45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,22 +1065,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1189,17 +1189,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,22 +1303,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1675,7 +1675,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2017,22 +2017,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2141,17 +2141,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2255,22 +2255,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2374,22 +2374,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2498,17 +2498,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2612,22 +2612,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2850,7 +2850,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2969,22 +2969,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3222,7 +3222,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3341,7 +3341,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3460,7 +3460,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3488,32 +3488,36 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3521,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>10:32</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3545,17 +3549,17 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
@@ -3565,12 +3569,12 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3603,32 +3607,36 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3636,7 +3644,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3660,37 +3668,37 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3718,32 +3726,36 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:53</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -3751,7 +3763,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3775,17 +3787,17 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
@@ -3795,17 +3807,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -3833,32 +3845,36 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -3866,7 +3882,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3890,37 +3906,37 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3948,32 +3964,36 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3981,7 +4001,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4005,37 +4025,37 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>79.3</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -4063,32 +4083,36 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4096,7 +4120,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4120,17 +4144,17 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
@@ -4140,17 +4164,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -4178,32 +4202,36 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4211,7 +4239,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4235,37 +4263,37 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -4293,32 +4321,36 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4326,7 +4358,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4350,17 +4382,17 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
@@ -4370,17 +4402,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -4441,7 +4473,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4480,7 +4512,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4523,32 +4555,36 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -4556,7 +4592,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4580,37 +4616,37 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -4671,7 +4707,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4725,7 +4761,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -4786,7 +4822,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4840,7 +4876,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4937,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4955,7 +4991,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -4963,22 +4999,22 @@
       <c r="A39" s="2" t="inlineStr"/>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>沪A35717D</t>
+          <t>沪A32298D</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -5011,12 +5047,12 @@
       <c r="M39" s="2" t="inlineStr"/>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>07:11</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>10:21</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5030,47 +5066,737 @@
       <c r="T39" s="2" t="inlineStr"/>
       <c r="U39" s="2" t="inlineStr">
         <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
           <t>11:30</t>
         </is>
       </c>
-      <c r="V39" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W39" s="2" t="inlineStr">
+      <c r="W40" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X39" s="2" t="inlineStr">
+      <c r="X40" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y39" s="2" t="inlineStr">
+      <c r="Y40" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z39" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AA39" s="2" t="inlineStr">
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>13/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>79.3</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>沪A08953A</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>11/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z43" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>82.3</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>沪A12050A</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB39" s="2" t="inlineStr">
-        <is>
-          <t>94.0</t>
-        </is>
-      </c>
-      <c r="AC39" s="2" t="inlineStr">
-        <is>
-          <t>12/14</t>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>06:12</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-24-182路.xlsx
+++ b/data/export/2026-09-24-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC45"/>
+  <dimension ref="A1:AC51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,12 +713,12 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,22 +1184,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA6" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1427,17 +1427,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,22 +1660,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1784,17 +1784,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2022,12 +2022,12 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2136,22 +2136,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2255,7 +2255,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2493,7 +2493,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2731,22 +2731,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2855,12 +2855,12 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3093,17 +3093,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3222,7 +3222,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3326,22 +3326,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3450,17 +3450,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:32</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3688,12 +3688,12 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3802,22 +3802,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3882,7 +3882,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3921,7 +3921,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3936,7 +3936,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4159,7 +4159,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4293,7 +4293,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -4331,24 +4331,24 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:35</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4358,7 +4358,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4397,22 +4397,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>78.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -4440,32 +4440,36 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
           <t>07:51</t>
@@ -4473,7 +4477,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4497,17 +4501,17 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
@@ -4517,12 +4521,12 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4565,24 +4569,24 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>70分钟</t>
+          <t>68分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4592,7 +4596,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4641,7 +4645,7 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>77.3</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4674,32 +4678,36 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4707,7 +4715,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4731,17 +4739,17 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
@@ -4751,17 +4759,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -4789,32 +4797,36 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -4822,7 +4834,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4846,37 +4858,37 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA37" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>75.7</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -4904,32 +4916,36 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4937,7 +4953,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4961,17 +4977,17 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
@@ -4981,17 +4997,17 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>81.3</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -5019,32 +5035,36 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -5052,7 +5072,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5076,17 +5096,17 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
@@ -5096,12 +5116,12 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -5134,32 +5154,36 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -5167,7 +5191,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5191,37 +5215,37 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -5282,7 +5306,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5397,7 +5421,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5436,7 +5460,7 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5451,7 +5475,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -5512,7 +5536,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5566,7 +5590,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -5627,7 +5651,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5671,12 +5695,12 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>71.5</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5742,7 +5766,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5791,12 +5815,702 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
+          <t>77.3</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>75.7</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>87.5</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>14/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>82.3</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>11/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>13:10</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>78.7</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>沪A08953A</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>13/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
           <t>78.0</t>
         </is>
       </c>
-      <c r="AC45" s="2" t="inlineStr">
-        <is>
-          <t>3/14</t>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-24-182路.xlsx
+++ b/data/export/2026-09-24-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC51"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,17 +1070,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,14 +1422,14 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
           <t>80.0</t>
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,14 +1779,14 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
           <t>81.3</t>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1898,17 +1898,17 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2260,17 +2260,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2379,17 +2379,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2617,17 +2617,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2850,17 +2850,17 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3088,14 +3088,14 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
           <t>80.0</t>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3222,7 +3222,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3445,14 +3445,14 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
           <t>81.3</t>
@@ -3460,7 +3460,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3564,17 +3564,17 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3693,12 +3693,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3763,7 +3763,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3817,7 +3817,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -3882,7 +3882,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3926,17 +3926,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4174,7 +4174,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -4239,7 +4239,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4283,17 +4283,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -4358,7 +4358,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4477,7 +4477,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4516,17 +4516,17 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4715,7 +4715,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4754,14 +4754,14 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
           <t>80.0</t>
@@ -4769,7 +4769,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -4834,7 +4834,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4953,7 +4953,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4992,14 +4992,14 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
           <t>81.3</t>
@@ -5007,7 +5007,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -5045,24 +5045,24 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>12:34</t>
+          <t>12:32</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>74分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -5072,7 +5072,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:31</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -5191,7 +5191,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5245,7 +5245,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -5273,32 +5273,36 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr"/>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M41" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -5306,7 +5310,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5330,17 +5334,17 @@
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y41" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z41" s="2" t="inlineStr">
@@ -5350,17 +5354,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>79.3</t>
+          <t>78.8</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -5388,32 +5392,36 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>67分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -5421,7 +5429,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5445,17 +5453,17 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
@@ -5465,17 +5473,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -5503,32 +5511,36 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -5536,7 +5548,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:12</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5560,17 +5572,17 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
@@ -5580,17 +5592,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -5618,32 +5630,36 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
           <t>07:51</t>
@@ -5651,7 +5667,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5675,32 +5691,32 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA44" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>71.5</t>
+          <t>72.3</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5733,32 +5749,36 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -5766,7 +5786,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5790,17 +5810,17 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
@@ -5810,12 +5830,12 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>77.3</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5881,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5963,32 +5983,36 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -5996,7 +6020,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6020,32 +6044,32 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>83.3</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
@@ -6111,7 +6135,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6165,7 +6189,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -6226,7 +6250,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6280,7 +6304,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -6341,7 +6365,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6385,17 +6409,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>78.3</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -6456,7 +6480,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6514,6 +6538,466 @@
         </is>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>沪A12050A</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>72.3</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>83.3</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>14/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>81.3</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>11/14</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-09-24-182路.xlsx
+++ b/data/export/2026-09-24-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC55"/>
+  <dimension ref="A1:AC59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1541,14 +1541,14 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
           <t>82.0</t>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1665,12 +1665,12 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2141,17 +2141,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2493,22 +2493,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:02</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3207,14 +3207,14 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
           <t>82.0</t>
@@ -3222,7 +3222,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3331,12 +3331,12 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3460,7 +3460,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3683,7 +3683,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3807,17 +3807,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3882,7 +3882,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3936,7 +3936,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4159,22 +4159,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -4358,7 +4358,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4397,7 +4397,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -4477,7 +4477,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4715,7 +4715,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4834,7 +4834,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4878,12 +4878,12 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -4953,7 +4953,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5007,7 +5007,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -5072,7 +5072,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:31</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5191,7 +5191,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5235,17 +5235,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -5429,7 +5429,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -5652,12 +5652,12 @@
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5667,7 +5667,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5759,24 +5759,24 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>71分钟</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -5786,7 +5786,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5835,7 +5835,7 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5868,32 +5868,36 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -5901,7 +5905,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5925,17 +5929,17 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
@@ -5945,12 +5949,12 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>75.7</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
@@ -6020,7 +6024,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6102,32 +6106,36 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:17</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -6135,7 +6143,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6159,17 +6167,17 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
@@ -6179,17 +6187,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>81.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -6217,32 +6225,36 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6250,7 +6262,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6274,37 +6286,37 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA49" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -6365,7 +6377,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6419,7 +6431,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -6480,7 +6492,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6519,7 +6531,7 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
@@ -6534,7 +6546,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -6595,7 +6607,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6710,7 +6722,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6825,7 +6837,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6940,7 +6952,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6994,7 +7006,467 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>79.5</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>76.5</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>沪A02126A</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>13/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>78.0</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-24-182路.xlsx
+++ b/data/export/2026-09-24-182路.xlsx
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3168,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4358,7 +4358,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4477,7 +4477,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4715,7 +4715,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4953,7 +4953,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5072,7 +5072,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5191,7 +5191,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5667,7 +5667,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -6024,7 +6024,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6262,7 +6262,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6377,7 +6377,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6492,7 +6492,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6607,7 +6607,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6722,7 +6722,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6837,7 +6837,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6952,7 +6952,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7067,7 +7067,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7182,7 +7182,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7297,7 +7297,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7412,7 +7412,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">

--- a/data/export/2026-09-24-182路.xlsx
+++ b/data/export/2026-09-24-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC59"/>
+  <dimension ref="A1:AC67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,12 +832,12 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,14 +1065,14 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
           <t>80.2</t>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1189,17 +1189,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,14 +1303,14 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
           <t>76.0</t>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,22 +1422,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,22 +1779,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1903,17 +1903,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2612,14 +2612,14 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
           <t>80.2</t>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2855,12 +2855,12 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2969,14 +2969,14 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
           <t>76.0</t>
@@ -2984,7 +2984,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3088,22 +3088,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3326,7 +3326,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3445,22 +3445,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3569,17 +3569,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3683,7 +3683,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3698,7 +3698,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3817,7 +3817,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3882,7 +3882,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3926,12 +3926,12 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -4001,7 +4001,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4040,7 +4040,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4164,12 +4164,12 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4278,14 +4278,14 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
           <t>80.2</t>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -4358,7 +4358,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4402,17 +4402,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -4477,7 +4477,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4635,14 +4635,14 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
           <t>76.0</t>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -4715,7 +4715,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4754,22 +4754,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -4834,7 +4834,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4953,7 +4953,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4992,22 +4992,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -5072,7 +5072,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -5245,7 +5245,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -5310,7 +5310,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5349,7 +5349,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5473,12 +5473,12 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5548,7 +5548,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13:12</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5587,14 +5587,14 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA43" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
           <t>80.2</t>
@@ -5602,7 +5602,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -5667,7 +5667,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5711,12 +5711,12 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5786,7 +5786,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5825,14 +5825,14 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA45" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
           <t>76.0</t>
@@ -5840,7 +5840,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -5905,7 +5905,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5944,7 +5944,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -6024,7 +6024,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -6197,7 +6197,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -6262,7 +6262,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6306,12 +6306,12 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6344,32 +6344,36 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -6377,7 +6381,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6401,17 +6405,17 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
@@ -6421,12 +6425,12 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>78.3</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6459,32 +6463,36 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>67分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6492,7 +6500,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6516,17 +6524,17 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
@@ -6536,17 +6544,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -6574,32 +6582,36 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
           <t>07:51</t>
@@ -6607,7 +6619,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6631,17 +6643,17 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
@@ -6651,12 +6663,12 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>72.3</t>
+          <t>72.5</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6689,32 +6701,36 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:16</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6722,7 +6738,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6746,37 +6762,37 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA53" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>79.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -6804,32 +6820,36 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6837,7 +6857,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6861,17 +6881,17 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
@@ -6881,17 +6901,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>83.3</t>
+          <t>81.8</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -6919,32 +6939,36 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6952,7 +6976,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6976,37 +7000,37 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA55" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>81.3</t>
+          <t>79.2</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -7067,7 +7091,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7106,7 +7130,7 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
@@ -7121,7 +7145,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -7149,32 +7173,36 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:53</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -7182,7 +7210,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7206,17 +7234,17 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
@@ -7226,12 +7254,12 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>75.8</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
@@ -7297,7 +7325,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7336,7 +7364,7 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA58" s="2" t="inlineStr">
@@ -7351,7 +7379,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -7412,7 +7440,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7456,17 +7484,937 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>78.0</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>78.8</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>06:12</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
           <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>79.2</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>80.2</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>11/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>79.5</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>10/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>16:01</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>75.0</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>沪A02126A</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>15:22</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>14/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-24-182路.xlsx
+++ b/data/export/2026-09-24-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC67"/>
+  <dimension ref="A1:AC74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1189,17 +1189,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,22 +1303,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1427,17 +1427,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1546,17 +1546,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1898,22 +1898,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2022,17 +2022,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2136,14 +2136,14 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
           <t>81.0</t>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2255,14 +2255,14 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
           <t>78.2</t>
@@ -2270,7 +2270,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2374,22 +2374,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2493,22 +2493,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2969,22 +2969,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3093,17 +3093,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3212,17 +3212,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3455,12 +3455,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3564,22 +3564,22 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3688,17 +3688,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3763,7 +3763,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3802,14 +3802,14 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
           <t>81.0</t>
@@ -3817,7 +3817,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -3882,7 +3882,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3921,14 +3921,14 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
           <t>78.2</t>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4040,22 +4040,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4159,22 +4159,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -4239,7 +4239,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4278,7 +4278,7 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA32" s="2" t="inlineStr">
@@ -4293,7 +4293,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -4358,7 +4358,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4402,17 +4402,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -4596,7 +4596,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4635,22 +4635,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -4715,7 +4715,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4759,17 +4759,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -4834,7 +4834,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4953,7 +4953,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5002,12 +5002,12 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -5072,7 +5072,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5116,17 +5116,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -5191,7 +5191,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5230,14 +5230,14 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
           <t>81.0</t>
@@ -5245,7 +5245,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -5310,7 +5310,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5349,22 +5349,22 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -5429,7 +5429,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5468,14 +5468,14 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
           <t>78.2</t>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -5548,7 +5548,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5587,7 +5587,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5602,7 +5602,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -5786,7 +5786,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5825,22 +5825,22 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA45" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -5905,7 +5905,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -6024,7 +6024,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6063,22 +6063,22 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -6143,7 +6143,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6182,14 +6182,14 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA48" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
           <t>81.0</t>
@@ -6197,7 +6197,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -6262,7 +6262,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6301,22 +6301,22 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA49" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -6381,7 +6381,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6420,14 +6420,14 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA50" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
           <t>78.2</t>
@@ -6435,7 +6435,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -6500,7 +6500,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6544,17 +6544,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6782,17 +6782,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -6830,19 +6830,19 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>15:36</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
@@ -6857,7 +6857,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6896,22 +6896,22 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA54" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>81.8</t>
+          <t>82.8</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -6949,24 +6949,24 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N55" s="2" t="inlineStr">
@@ -6976,7 +6976,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -7058,32 +7058,36 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -7091,7 +7095,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7115,17 +7119,17 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
@@ -7135,17 +7139,17 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -7183,24 +7187,24 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>15:53</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>73分钟</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N57" s="2" t="inlineStr">
@@ -7210,7 +7214,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7249,22 +7253,22 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA57" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>75.8</t>
+          <t>76.2</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -7292,32 +7296,36 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:09</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>69分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -7325,7 +7333,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7349,17 +7357,17 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
@@ -7369,17 +7377,17 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>77.7</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -7407,32 +7415,36 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -7440,7 +7452,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7464,17 +7476,17 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
@@ -7484,17 +7496,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -7522,32 +7534,36 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -7555,7 +7571,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7579,37 +7595,37 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA60" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>78.8</t>
+          <t>77.6</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -7637,32 +7653,36 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -7670,7 +7690,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7694,17 +7714,17 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
@@ -7714,17 +7734,17 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -7752,32 +7772,36 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:43</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -7785,7 +7809,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7809,37 +7833,37 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA62" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -7900,7 +7924,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7949,12 +7973,12 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>79.2</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -8015,7 +8039,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8054,7 +8078,7 @@
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA64" s="2" t="inlineStr">
@@ -8069,7 +8093,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -8087,7 +8111,7 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -8130,7 +8154,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8144,7 +8168,7 @@
       <c r="T65" s="2" t="inlineStr"/>
       <c r="U65" s="2" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="V65" s="2" t="inlineStr">
@@ -8174,17 +8198,17 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>78.6</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -8245,7 +8269,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8307,22 +8331,22 @@
       <c r="A67" s="2" t="inlineStr"/>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>沪A02126A</t>
+          <t>沪A35717D</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
-        <is>
-          <t>16:20</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -8355,12 +8379,12 @@
       <c r="M67" s="2" t="inlineStr"/>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>06:21</t>
+          <t>07:11</t>
         </is>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>16:22</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8374,47 +8398,852 @@
       <c r="T67" s="2" t="inlineStr"/>
       <c r="U67" s="2" t="inlineStr">
         <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>13/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>沪A02126A</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
           <t>16:20</t>
         </is>
       </c>
-      <c r="V67" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>06:21</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W67" s="2" t="inlineStr">
+      <c r="W68" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X67" s="2" t="inlineStr">
+      <c r="X68" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y67" s="2" t="inlineStr">
+      <c r="Y68" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z67" s="2" t="inlineStr">
+      <c r="Z68" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA67" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB67" s="2" t="inlineStr">
-        <is>
-          <t>82.0</t>
-        </is>
-      </c>
-      <c r="AC67" s="2" t="inlineStr">
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>77.7</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>7/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>82.8</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
         <is>
           <t>14/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>16:36</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>76.2</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>77.6</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>6/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A08953A</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>16:48</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>78.2</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>06:12</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>75.4</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>16:22</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>80.2</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>12/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-24-182路.xlsx
+++ b/data/export/2026-09-24-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC74"/>
+  <dimension ref="A1:AC82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,17 +1070,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,22 +1422,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1546,17 +1546,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,17 +1660,17 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,17 +1779,17 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2017,22 +2017,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2617,17 +2617,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2850,7 +2850,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3088,22 +3088,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3212,17 +3212,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3326,17 +3326,17 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3445,17 +3445,17 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3683,22 +3683,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3763,7 +3763,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3817,7 +3817,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3882,7 +3882,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3936,7 +3936,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4283,17 +4283,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -4358,7 +4358,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4397,7 +4397,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4477,7 +4477,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4516,7 +4516,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4715,7 +4715,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4754,22 +4754,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -4834,7 +4834,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4873,17 +4873,17 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA37" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -4953,7 +4953,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4992,17 +4992,17 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5072,7 +5072,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5111,22 +5111,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -5191,7 +5191,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5230,7 +5230,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5245,7 +5245,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -5310,7 +5310,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -5548,7 +5548,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5592,17 +5592,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -5667,7 +5667,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5706,7 +5706,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5786,7 +5786,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5905,7 +5905,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5944,17 +5944,17 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA46" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
@@ -6024,7 +6024,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6063,7 +6063,7 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA47" s="2" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6182,7 +6182,7 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -6197,7 +6197,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -6262,7 +6262,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6381,7 +6381,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6435,7 +6435,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -6500,7 +6500,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6539,7 +6539,7 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
@@ -6619,7 +6619,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6658,7 +6658,7 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6777,22 +6777,22 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA53" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -6857,7 +6857,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6896,7 +6896,7 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
@@ -6976,7 +6976,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7015,17 +7015,17 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA55" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
@@ -7095,7 +7095,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7134,22 +7134,22 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA56" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -7214,7 +7214,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7333,7 +7333,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7377,17 +7377,17 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -7452,7 +7452,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7491,7 +7491,7 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
@@ -7571,7 +7571,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7663,24 +7663,24 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>16:43</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>83分钟</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N61" s="2" t="inlineStr">
@@ -7690,7 +7690,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7729,22 +7729,22 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA61" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -7809,7 +7809,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7891,32 +7891,36 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -7924,7 +7928,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7948,32 +7952,32 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA63" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>80.2</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
@@ -8006,32 +8010,36 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8039,7 +8047,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8063,17 +8071,17 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
@@ -8083,17 +8091,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>79.8</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -8121,32 +8129,36 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8154,7 +8166,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8178,37 +8190,37 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA65" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>78.6</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -8236,32 +8248,36 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -8269,7 +8285,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8293,32 +8309,32 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA66" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>74.8</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
@@ -8384,7 +8400,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8423,7 +8439,7 @@
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
@@ -8438,7 +8454,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -8466,32 +8482,36 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
           <t>06:21</t>
@@ -8499,7 +8519,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8523,17 +8543,17 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr">
@@ -8543,17 +8563,17 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>77.7</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -8614,7 +8634,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8653,7 +8673,7 @@
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
@@ -8729,7 +8749,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8844,7 +8864,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8959,7 +8979,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9013,7 +9033,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -9021,22 +9041,22 @@
       <c r="A73" s="2" t="inlineStr"/>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>沪A68870D</t>
+          <t>沪A67983D</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
           <t>金杨路金口路</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="E73" s="2" t="inlineStr">
-        <is>
-          <t>川沙客运站</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -9069,12 +9089,12 @@
       <c r="M73" s="2" t="inlineStr"/>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>06:12</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9123,12 +9143,12 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>75.6</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -9136,7 +9156,7 @@
       <c r="A74" s="2" t="inlineStr"/>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>沪A31073D</t>
+          <t>沪A68870D</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -9146,7 +9166,7 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
@@ -9184,12 +9204,12 @@
       <c r="M74" s="2" t="inlineStr"/>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:12</t>
         </is>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>16:22</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9203,47 +9223,967 @@
       <c r="T74" s="2" t="inlineStr"/>
       <c r="U74" s="2" t="inlineStr">
         <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>75.4</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>沪A12050A</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
           <t>17:15</t>
         </is>
       </c>
-      <c r="V74" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W74" s="2" t="inlineStr">
+      <c r="W75" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X74" s="2" t="inlineStr">
+      <c r="X75" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y74" s="2" t="inlineStr">
+      <c r="Y75" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z74" s="2" t="inlineStr">
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>72.5</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>沪A31073D</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA74" s="2" t="inlineStr">
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>79.8</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
+          <t>9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>沪A13735A</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>13/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>74.8</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB74" s="2" t="inlineStr">
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>81.0</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>12/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
         <is>
           <t>80.2</t>
         </is>
       </c>
-      <c r="AC74" s="2" t="inlineStr">
-        <is>
-          <t>12/14</t>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>10/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A67026D</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>18:01</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>18:01</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>82.8</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>14/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>79.5</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-24-182路.xlsx
+++ b/data/export/2026-09-24-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC82"/>
+  <dimension ref="A1:AC89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,22 +1303,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,7 +1660,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1903,17 +1903,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2141,17 +2141,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2255,22 +2255,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2374,22 +2374,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2493,22 +2493,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2850,7 +2850,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2969,22 +2969,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3326,7 +3326,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3460,7 +3460,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3569,17 +3569,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3693,12 +3693,12 @@
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3763,7 +3763,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3807,17 +3807,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -3882,7 +3882,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3921,22 +3921,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4040,22 +4040,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4159,22 +4159,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -4239,7 +4239,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4293,7 +4293,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -4358,7 +4358,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4397,7 +4397,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -4477,7 +4477,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4516,7 +4516,7 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA34" s="2" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4635,22 +4635,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -4715,7 +4715,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4769,7 +4769,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -4834,7 +4834,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4953,7 +4953,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5007,7 +5007,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -5072,7 +5072,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5121,12 +5121,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -5191,7 +5191,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5235,17 +5235,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -5310,7 +5310,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5349,22 +5349,22 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA41" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -5429,7 +5429,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5468,22 +5468,22 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -5548,7 +5548,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5602,7 +5602,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -5667,7 +5667,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5706,7 +5706,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5786,7 +5786,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5825,22 +5825,22 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA45" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -5905,7 +5905,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5944,7 +5944,7 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA46" s="2" t="inlineStr">
@@ -6024,7 +6024,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -6143,7 +6143,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6187,17 +6187,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -6262,7 +6262,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6301,22 +6301,22 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA49" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -6381,7 +6381,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6420,22 +6420,22 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA50" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -6500,7 +6500,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6539,7 +6539,7 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
@@ -6554,7 +6554,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -6619,7 +6619,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6658,7 +6658,7 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6792,7 +6792,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -6857,7 +6857,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6901,17 +6901,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -6976,7 +6976,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7030,7 +7030,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -7095,7 +7095,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7144,12 +7144,12 @@
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -7214,7 +7214,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7253,22 +7253,22 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA57" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -7333,7 +7333,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7387,7 +7387,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -7452,7 +7452,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7491,7 +7491,7 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
@@ -7506,7 +7506,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -7571,7 +7571,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7610,22 +7610,22 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA60" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -7690,7 +7690,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7744,7 +7744,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -7809,7 +7809,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7848,22 +7848,22 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA62" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -7928,7 +7928,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7982,7 +7982,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -8047,7 +8047,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8101,7 +8101,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -8139,24 +8139,24 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>17:25</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -8166,7 +8166,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8215,12 +8215,12 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>80.7</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -8285,7 +8285,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8324,7 +8324,7 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
@@ -8367,32 +8367,36 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M67" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -8400,7 +8404,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8424,17 +8428,17 @@
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z67" s="2" t="inlineStr">
@@ -8444,17 +8448,17 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -8519,7 +8523,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8573,7 +8577,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -8601,32 +8605,36 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8634,7 +8642,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8658,17 +8666,17 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr">
@@ -8678,17 +8686,17 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -8716,32 +8724,36 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8749,7 +8761,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8773,37 +8785,37 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA70" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>76.2</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -8831,32 +8843,36 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>105分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M71" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8864,7 +8880,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8888,37 +8904,37 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA71" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>77.6</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -8946,32 +8962,36 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:17</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M72" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
           <t>07:21</t>
@@ -8979,7 +8999,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9003,37 +9023,37 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA72" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>80.4</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -9094,7 +9114,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9133,7 +9153,7 @@
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA73" s="2" t="inlineStr">
@@ -9148,7 +9168,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -9176,32 +9196,36 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>100分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M74" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -9209,7 +9233,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9233,37 +9257,37 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA74" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>79.5</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -9324,7 +9348,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9363,7 +9387,7 @@
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA75" s="2" t="inlineStr">
@@ -9439,7 +9463,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9493,7 +9517,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -9554,7 +9578,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9608,7 +9632,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -9669,7 +9693,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9708,7 +9732,7 @@
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr">
@@ -9784,7 +9808,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9828,17 +9852,17 @@
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>81.0</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -9899,7 +9923,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9953,7 +9977,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -10014,7 +10038,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10058,17 +10082,17 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>82.8</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -10129,7 +10153,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10178,12 +10202,817 @@
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
+          <t>80.7</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>10/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>沪A55712D</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>18:15</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>78.7</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>沪A08953A</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>18:31</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>07:21</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>18:31</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>80.4</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>82.2</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>14/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>沪A67983D</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>75.6</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>3/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr"/>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>沪A12050A</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>07:51</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>72.5</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>06:12</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
           <t>79.5</t>
         </is>
       </c>
-      <c r="AC82" s="2" t="inlineStr">
-        <is>
-          <t>8/14</t>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>74.8</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>2/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-24-182路.xlsx
+++ b/data/export/2026-09-24-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC89"/>
+  <dimension ref="A1:AC94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1026,7 +1026,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1070,17 +1070,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1199,7 +1199,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1308,17 +1308,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1422,22 +1422,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1665,17 +1665,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1779,22 +1779,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2136,22 +2136,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2617,17 +2617,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2855,17 +2855,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2974,17 +2974,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3088,22 +3088,22 @@
       </c>
       <c r="Z22" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA22" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -3222,7 +3222,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3331,17 +3331,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3445,22 +3445,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3579,7 +3579,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3683,7 +3683,7 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
@@ -3698,7 +3698,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3763,7 +3763,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3802,22 +3802,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -3882,7 +3882,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3936,7 +3936,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4040,7 +4040,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -4055,7 +4055,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4283,17 +4283,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -4358,7 +4358,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4412,7 +4412,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -4477,7 +4477,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4521,17 +4521,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -4596,7 +4596,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4640,17 +4640,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -4715,7 +4715,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4754,22 +4754,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -4834,7 +4834,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4878,17 +4878,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -4953,7 +4953,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4992,22 +4992,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA38" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -5072,7 +5072,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA39" s="2" t="inlineStr">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -5191,7 +5191,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5230,22 +5230,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -5310,7 +5310,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5349,7 +5349,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5364,7 +5364,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -5429,7 +5429,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -5548,7 +5548,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5592,17 +5592,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -5667,7 +5667,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5711,17 +5711,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -5786,7 +5786,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5830,17 +5830,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -5905,7 +5905,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5949,17 +5949,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -6024,7 +6024,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -6143,7 +6143,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6182,22 +6182,22 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA48" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -6262,7 +6262,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6381,7 +6381,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6435,7 +6435,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -6500,7 +6500,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6554,7 +6554,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -6619,7 +6619,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6663,17 +6663,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6777,22 +6777,22 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA53" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -6857,7 +6857,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6911,7 +6911,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -6976,7 +6976,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7015,22 +7015,22 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA55" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -7095,7 +7095,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7134,7 +7134,7 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA56" s="2" t="inlineStr">
@@ -7149,7 +7149,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -7214,7 +7214,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7387,7 +7387,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -7452,7 +7452,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7506,7 +7506,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -7571,7 +7571,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7610,7 +7610,7 @@
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
@@ -7625,7 +7625,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -7690,7 +7690,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7729,22 +7729,22 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA61" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -7809,7 +7809,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7853,17 +7853,17 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -7928,7 +7928,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7967,22 +7967,22 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA63" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -8047,7 +8047,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8091,17 +8091,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -8166,7 +8166,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8205,7 +8205,7 @@
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA65" s="2" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -8285,7 +8285,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8329,17 +8329,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -8404,7 +8404,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8443,22 +8443,22 @@
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA67" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -8577,7 +8577,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -8642,7 +8642,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8696,7 +8696,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -8761,7 +8761,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8880,7 +8880,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8919,7 +8919,7 @@
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA71" s="2" t="inlineStr">
@@ -8934,7 +8934,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -8999,7 +8999,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9053,7 +9053,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -9114,7 +9114,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9168,7 +9168,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -9196,36 +9196,32 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>18:40</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>100分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M74" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
       <c r="N74" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -9233,7 +9229,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9257,17 +9253,17 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
@@ -9277,17 +9273,17 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -9315,32 +9311,36 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:49</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
           <t>07:51</t>
@@ -9348,7 +9348,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9372,17 +9372,17 @@
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
@@ -9392,17 +9392,17 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -9430,32 +9430,36 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:08</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>113分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9463,7 +9467,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9487,17 +9491,17 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
@@ -9507,17 +9511,17 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>79.8</t>
+          <t>85.3</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -9545,32 +9549,36 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:13</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>103分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9578,7 +9586,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9602,37 +9610,37 @@
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA77" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -9660,32 +9668,36 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:16</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>106分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -9693,7 +9705,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9717,17 +9729,17 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
@@ -9737,17 +9749,17 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>74.8</t>
+          <t>80.0</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -9775,32 +9787,36 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:38</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>113分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M79" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -9808,7 +9824,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9832,37 +9848,37 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA79" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -9890,32 +9906,36 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:22</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M80" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9923,7 +9943,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9947,37 +9967,37 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA80" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>80.2</t>
+          <t>82.2</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -10038,7 +10058,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10092,7 +10112,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -10153,7 +10173,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10192,7 +10212,7 @@
       </c>
       <c r="Z82" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA82" s="2" t="inlineStr">
@@ -10207,7 +10227,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -10268,7 +10288,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10383,7 +10403,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10437,7 +10457,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -10498,7 +10518,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10537,7 +10557,7 @@
       </c>
       <c r="Z85" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA85" s="2" t="inlineStr">
@@ -10552,7 +10572,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -10613,7 +10633,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10667,7 +10687,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -10728,7 +10748,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10772,17 +10792,17 @@
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>72.5</t>
+          <t>76.8</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>1/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -10843,7 +10863,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10887,17 +10907,17 @@
       </c>
       <c r="AA88" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>79.5</t>
+          <t>75.4</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>1/14</t>
         </is>
       </c>
     </row>
@@ -10905,22 +10925,22 @@
       <c r="A89" s="2" t="inlineStr"/>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>沪A66513D</t>
+          <t>沪A13735A</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
           <t>川沙客运站</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="E89" s="2" t="inlineStr">
-        <is>
-          <t>金杨路金口路</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
@@ -10953,12 +10973,12 @@
       <c r="M89" s="2" t="inlineStr"/>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>06:41</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>19:21</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -10972,47 +10992,622 @@
       <c r="T89" s="2" t="inlineStr"/>
       <c r="U89" s="2" t="inlineStr">
         <is>
+          <t>19:15</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>85.5</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>13/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr"/>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
           <t>19:30</t>
         </is>
       </c>
-      <c r="V89" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W89" s="2" t="inlineStr">
+      <c r="W90" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X89" s="2" t="inlineStr">
+      <c r="X90" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y89" s="2" t="inlineStr">
+      <c r="Y90" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z89" s="2" t="inlineStr">
+      <c r="Z90" s="2" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA89" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB89" s="2" t="inlineStr">
-        <is>
-          <t>74.8</t>
-        </is>
-      </c>
-      <c r="AC89" s="2" t="inlineStr">
-        <is>
-          <t>2/14</t>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>5/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr"/>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>沪A67353D</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>82.2</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>10/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr"/>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>沪A32298D</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>80.7</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>8/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr"/>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>19:55</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr"/>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>19:55</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>86.2</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>14/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>沪A68397D</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>20:10</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>82.2</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>10/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-24-182路.xlsx
+++ b/data/export/2026-09-24-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC94"/>
+  <dimension ref="A1:AC95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,12 +713,12 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1903,17 +1903,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2022,12 +2022,12 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2151,7 +2151,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA21" s="2" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3460,7 +3460,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3569,17 +3569,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -3644,7 +3644,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3688,12 +3688,12 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3817,7 +3817,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -3882,7 +3882,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -4001,7 +4001,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4055,7 +4055,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4293,7 +4293,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -4358,7 +4358,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4477,7 +4477,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4635,7 +4635,7 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA35" s="2" t="inlineStr">
@@ -4715,7 +4715,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4769,7 +4769,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -4834,7 +4834,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4953,7 +4953,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5007,7 +5007,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -5072,7 +5072,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -5191,7 +5191,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5245,7 +5245,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -5310,7 +5310,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5364,7 +5364,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -5429,7 +5429,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5602,7 +5602,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -5667,7 +5667,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5786,7 +5786,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5825,7 +5825,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -5905,7 +5905,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -6024,7 +6024,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -6143,7 +6143,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6197,7 +6197,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -6262,7 +6262,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6381,7 +6381,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6500,7 +6500,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6619,7 +6619,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6738,7 +6738,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6792,7 +6792,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -6857,7 +6857,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6901,17 +6901,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -6976,7 +6976,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7030,7 +7030,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -7095,7 +7095,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
@@ -7214,7 +7214,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7452,7 +7452,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7571,7 +7571,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7625,7 +7625,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -7690,7 +7690,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7744,7 +7744,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -7809,7 +7809,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7848,7 +7848,7 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
@@ -7928,7 +7928,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7982,7 +7982,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -8101,7 +8101,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -8166,7 +8166,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
@@ -8285,7 +8285,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8404,7 +8404,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8458,7 +8458,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -8642,7 +8642,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8686,17 +8686,17 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -8761,7 +8761,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8880,7 +8880,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8934,7 +8934,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -8999,7 +8999,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9229,7 +9229,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9268,7 +9268,7 @@
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr">
@@ -9348,7 +9348,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9521,7 +9521,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -9586,7 +9586,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9640,7 +9640,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -9705,7 +9705,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9824,7 +9824,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9878,7 +9878,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -9943,7 +9943,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9997,7 +9997,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -10025,32 +10025,36 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>109分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M81" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10058,7 +10062,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10082,17 +10086,17 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr">
@@ -10102,17 +10106,17 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>14/14</t>
         </is>
       </c>
     </row>
@@ -10140,32 +10144,36 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:41</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M82" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10173,7 +10181,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10197,17 +10205,17 @@
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z82" s="2" t="inlineStr">
@@ -10217,12 +10225,12 @@
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
@@ -10288,7 +10296,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10403,7 +10411,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10518,7 +10526,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10572,7 +10580,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -10633,7 +10641,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10748,7 +10756,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10863,7 +10871,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10902,7 +10910,7 @@
       </c>
       <c r="Z88" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA88" s="2" t="inlineStr">
@@ -10978,7 +10986,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11032,7 +11040,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -11093,7 +11101,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11208,7 +11216,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11262,7 +11270,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -11323,7 +11331,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11367,12 +11375,12 @@
       </c>
       <c r="AA92" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>80.7</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
@@ -11438,7 +11446,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11492,7 +11500,7 @@
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>14/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -11553,7 +11561,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:21</t>
+          <t>19:32</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11607,7 +11615,122 @@
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>10/14</t>
+          <t>9/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr"/>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>沪A68870D</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>06:12</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>19:32</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr"/>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>75.4</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>1/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-24-182路.xlsx
+++ b/data/export/2026-09-24-182路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC95"/>
+  <dimension ref="A1:AC97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1189,17 +1189,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1660,22 +1660,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2136,7 +2136,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2270,7 +2270,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2379,12 +2379,12 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2498,17 +2498,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -2811,7 +2811,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2855,17 +2855,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3326,22 +3326,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA24" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3460,7 +3460,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -3525,7 +3525,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3698,7 +3698,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -3763,7 +3763,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3802,7 +3802,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3936,7 +3936,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4164,17 +4164,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -4358,7 +4358,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4402,17 +4402,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -4477,7 +4477,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4521,17 +4521,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -4596,7 +4596,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4715,7 +4715,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4834,7 +4834,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4873,22 +4873,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA37" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -4953,7 +4953,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5007,7 +5007,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -5072,7 +5072,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -5191,7 +5191,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5230,7 +5230,7 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
@@ -5310,7 +5310,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5354,12 +5354,12 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -5667,7 +5667,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5711,17 +5711,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -5786,7 +5786,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5830,12 +5830,12 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5905,7 +5905,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5944,22 +5944,22 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA46" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -6024,7 +6024,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6182,7 +6182,7 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -6262,7 +6262,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6306,17 +6306,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -6381,7 +6381,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6435,7 +6435,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -6500,7 +6500,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6544,17 +6544,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -6619,7 +6619,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6663,17 +6663,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6857,7 +6857,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6976,7 +6976,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7030,7 +7030,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -7095,7 +7095,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7149,7 +7149,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -7214,7 +7214,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7258,17 +7258,17 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -7387,7 +7387,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -7452,7 +7452,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7496,17 +7496,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -7571,7 +7571,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
@@ -7690,7 +7690,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7809,7 +7809,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7853,12 +7853,12 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
@@ -7928,7 +7928,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7982,7 +7982,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -8166,7 +8166,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -8285,7 +8285,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8324,22 +8324,22 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA66" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -8404,7 +8404,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8443,7 +8443,7 @@
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
@@ -8577,7 +8577,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -8642,7 +8642,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8761,7 +8761,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8805,17 +8805,17 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -8880,7 +8880,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8924,12 +8924,12 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
@@ -8999,7 +8999,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9053,7 +9053,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -9114,7 +9114,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9158,17 +9158,17 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -9229,7 +9229,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9273,12 +9273,12 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
@@ -9348,7 +9348,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9392,17 +9392,17 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -9586,7 +9586,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9705,7 +9705,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9744,22 +9744,22 @@
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA78" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -9824,7 +9824,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9863,7 +9863,7 @@
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
@@ -9943,7 +9943,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9997,7 +9997,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -10047,12 +10047,12 @@
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -10062,7 +10062,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10181,7 +10181,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10235,7 +10235,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -10263,32 +10263,36 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:53</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>98分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M83" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10296,7 +10300,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10320,17 +10324,17 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y83" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z83" s="2" t="inlineStr">
@@ -10340,17 +10344,17 @@
       </c>
       <c r="AA83" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>81.4</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>4/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -10411,7 +10415,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>19:51</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10465,7 +10469,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>6/14</t>
+          <t>5/14</t>
         </is>
       </c>
     </row>
@@ -10493,32 +10497,36 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:58</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M85" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10526,7 +10534,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10550,17 +10558,17 @@
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z85" s="2" t="inlineStr">
@@ -10570,12 +10578,12 @@
       </c>
       <c r="AA85" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
@@ -10608,32 +10616,36 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M86" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10641,7 +10653,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10665,17 +10677,17 @@
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y86" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z86" s="2" t="inlineStr">
@@ -10685,17 +10697,17 @@
       </c>
       <c r="AA86" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>75.6</t>
+          <t>77.8</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>2/14</t>
+          <t>3/14</t>
         </is>
       </c>
     </row>
@@ -10723,32 +10735,36 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:14</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M87" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
           <t>07:51</t>
@@ -10756,7 +10772,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:12</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10780,17 +10796,17 @@
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z87" s="2" t="inlineStr">
@@ -10800,17 +10816,17 @@
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>76.8</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>3/14</t>
+          <t>2/14</t>
         </is>
       </c>
     </row>
@@ -10838,32 +10854,36 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:21</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M88" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -10871,7 +10891,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10895,17 +10915,17 @@
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y88" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z88" s="2" t="inlineStr">
@@ -10915,12 +10935,12 @@
       </c>
       <c r="AA88" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
@@ -10986,7 +11006,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11068,32 +11088,36 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:41</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>71分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M90" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -11101,7 +11125,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11125,37 +11149,37 @@
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y90" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z90" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="AA90" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>5/14</t>
+          <t>4/14</t>
         </is>
       </c>
     </row>
@@ -11216,7 +11240,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11270,7 +11294,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>10/14</t>
         </is>
       </c>
     </row>
@@ -11331,7 +11355,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11385,7 +11409,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>8/14</t>
+          <t>7/14</t>
         </is>
       </c>
     </row>
@@ -11446,7 +11470,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11485,7 +11509,7 @@
       </c>
       <c r="Z93" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AA93" s="2" t="inlineStr">
@@ -11561,7 +11585,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11605,12 +11629,12 @@
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
@@ -11676,7 +11700,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>19:32</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11720,17 +11744,247 @@
       </c>
       <c r="AA95" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>75.4</t>
+          <t>75.5</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
           <t>1/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr"/>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>沪A66513D</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>20:50</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>06:41</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>20:22</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>20:50</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>78.7</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>4/14</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr"/>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>沪A35717D</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>金杨路金口路</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>21:15</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>川沙客运站</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>07:11</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>20:22</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr"/>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>21:15</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>86.2</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>13/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-24-182路.xlsx
+++ b/data/export/2026-09-24-182路.xlsx
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1427,17 +1427,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1740,7 +1740,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1784,12 +1784,12 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2022,17 +2022,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2141,17 +2141,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -2335,7 +2335,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2379,17 +2379,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3093,17 +3093,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB22" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3688,17 +3688,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -3763,7 +3763,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3807,17 +3807,17 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -4001,7 +4001,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -4174,7 +4174,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -4596,7 +4596,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4715,7 +4715,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4759,17 +4759,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -4834,7 +4834,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4953,7 +4953,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4997,12 +4997,12 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5072,7 +5072,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5116,17 +5116,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -5191,7 +5191,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5235,17 +5235,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -5310,7 +5310,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5354,17 +5354,17 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -5602,7 +5602,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -5786,7 +5786,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5830,12 +5830,12 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5905,7 +5905,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6187,17 +6187,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -6316,7 +6316,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -6738,7 +6738,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6782,17 +6782,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -6976,7 +6976,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7020,12 +7020,12 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
@@ -7095,7 +7095,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7139,17 +7139,17 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -7268,7 +7268,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -7571,7 +7571,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7615,17 +7615,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -7690,7 +7690,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7734,17 +7734,17 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -7809,7 +7809,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7853,12 +7853,12 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
@@ -7928,7 +7928,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7972,12 +7972,12 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
@@ -8101,7 +8101,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -8166,7 +8166,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8210,17 +8210,17 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -8285,7 +8285,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8404,7 +8404,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8448,17 +8448,17 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -8815,7 +8815,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -8880,7 +8880,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8924,17 +8924,17 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -9229,7 +9229,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9273,12 +9273,12 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
@@ -9521,7 +9521,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>11/14</t>
+          <t>12/14</t>
         </is>
       </c>
     </row>
@@ -9586,7 +9586,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9630,17 +9630,17 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -9705,7 +9705,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9824,7 +9824,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9868,17 +9868,17 @@
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -9943,7 +9943,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9987,12 +9987,12 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
@@ -10181,7 +10181,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10225,17 +10225,17 @@
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -10354,7 +10354,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>9/14</t>
         </is>
       </c>
     </row>
@@ -10534,7 +10534,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10578,17 +10578,17 @@
       </c>
       <c r="AA85" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -10891,7 +10891,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10935,12 +10935,12 @@
       </c>
       <c r="AA88" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
@@ -10973,32 +10973,36 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M89" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11006,7 +11010,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11030,17 +11034,17 @@
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y89" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z89" s="2" t="inlineStr">
@@ -11050,17 +11054,17 @@
       </c>
       <c r="AA89" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>12/14</t>
+          <t>13/14</t>
         </is>
       </c>
     </row>
@@ -11125,7 +11129,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11207,32 +11211,36 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:50</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M91" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11240,7 +11248,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>20:42</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11264,17 +11272,17 @@
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y91" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z91" s="2" t="inlineStr">
@@ -11284,12 +11292,12 @@
       </c>
       <c r="AA91" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>82.2</t>
+          <t>81.9</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
@@ -11322,32 +11330,36 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:05</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M92" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11355,7 +11367,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:02</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11379,17 +11391,17 @@
       </c>
       <c r="W92" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z92" s="2" t="inlineStr">
@@ -11399,17 +11411,17 @@
       </c>
       <c r="AA92" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>81.4</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>7/14</t>
+          <t>8/14</t>
         </is>
       </c>
     </row>
@@ -11437,32 +11449,36 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:08</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M93" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
           <t>07:11</t>
@@ -11470,7 +11486,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11494,17 +11510,17 @@
       </c>
       <c r="W93" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z93" s="2" t="inlineStr">
@@ -11514,17 +11530,17 @@
       </c>
       <c r="AA93" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>
@@ -11552,32 +11568,36 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:23</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M94" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11585,7 +11605,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11609,17 +11629,17 @@
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
@@ -11629,17 +11649,17 @@
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>9/14</t>
+          <t>6/14</t>
         </is>
       </c>
     </row>
@@ -11667,32 +11687,36 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:42</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M95" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
           <t>06:12</t>
@@ -11700,7 +11724,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11724,17 +11748,17 @@
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z95" s="2" t="inlineStr">
@@ -11744,12 +11768,12 @@
       </c>
       <c r="AA95" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
@@ -11815,7 +11839,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11930,7 +11954,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>20:22</t>
+          <t>21:21</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11974,17 +11998,17 @@
       </c>
       <c r="AA97" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>13/14</t>
+          <t>11/14</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-24-182路.xlsx
+++ b/data/export/2026-09-24-182路.xlsx
@@ -1264,7 +1264,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1665,12 +1665,12 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -2097,7 +2097,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2930,7 +2930,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3331,12 +3331,12 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4834,7 +4834,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4878,12 +4878,12 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
@@ -5191,7 +5191,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5786,7 +5786,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5905,7 +5905,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5949,12 +5949,12 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -7809,7 +7809,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -8285,7 +8285,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8329,12 +8329,12 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
@@ -8404,7 +8404,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -9229,7 +9229,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9705,7 +9705,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9749,12 +9749,12 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
@@ -9824,7 +9824,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -10891,7 +10891,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -11129,7 +11129,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="AA90" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
@@ -11486,7 +11486,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11709,12 +11709,12 @@
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -11724,7 +11724,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:41</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11806,32 +11806,36 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:02</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>72分钟</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M96" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
           <t>06:41</t>
@@ -11839,7 +11843,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11863,17 +11867,17 @@
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y96" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z96" s="2" t="inlineStr">
@@ -11883,12 +11887,12 @@
       </c>
       <c r="AA96" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>78.7</t>
+          <t>77.9</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
@@ -11954,7 +11958,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>21:21</t>
+          <t>21:52</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
